--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. PUERTO SAGUNTO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. PUERTO SAGUNTO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Q. GJENERALI</t>
+          <t>M. TORTAROLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>4.047800000000001</v>
+        <v>13.9368</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4654</v>
+        <v>11.9897</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5823</v>
+        <v>1.9472</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9308</v>
+        <v>6.196899999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08610000000000007</v>
+        <v>-3.4704</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8447</v>
+        <v>9.667299999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4689</v>
+        <v>12.859</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8651000000000001</v>
+        <v>-0.2405999999999997</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6037</v>
+        <v>13.0995</v>
       </c>
       <c r="M2" t="n">
-        <v>0.462</v>
+        <v>-6.6622</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.779</v>
+        <v>-3.2299</v>
       </c>
       <c r="O2" t="n">
-        <v>1.241</v>
+        <v>-3.4324</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8002</v>
+        <v>3.1158</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.201</v>
+        <v>-8.5684</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4006</v>
+        <v>11.6842</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09720000000000018</v>
+        <v>-3.036</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5381</v>
+        <v>-0.9946999999999998</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4409999999999999</v>
+        <v>-2.041</v>
       </c>
       <c r="V2" t="n">
-        <v>2.82</v>
+        <v>7.6601</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6594</v>
+        <v>8.693899999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1606</v>
+        <v>-1.0338</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>3.011099999999999</v>
+        <v>5.2432</v>
       </c>
       <c r="E3" t="n">
-        <v>5.447900000000001</v>
+        <v>5.9926</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.4368</v>
+        <v>-0.7494000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7829999999999999</v>
+        <v>4.2952</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.0853</v>
+        <v>-3.7302</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3023</v>
+        <v>8.025399999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>2.32</v>
+        <v>6.595800000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8052999999999999</v>
+        <v>-0.4976</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1252</v>
+        <v>7.0934</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.1029</v>
+        <v>-2.3005</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.28</v>
+        <v>-3.2326</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.823</v>
+        <v>0.9319999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2001000000000002</v>
+        <v>3.8947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.401</v>
+        <v>-3.8948</v>
       </c>
       <c r="R3" t="n">
-        <v>3.601</v>
+        <v>7.7895</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8146</v>
+        <v>-5.2176</v>
       </c>
       <c r="T3" t="n">
-        <v>3.0902</v>
+        <v>-3.1664</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2756</v>
+        <v>-2.0513</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7794000000000003</v>
+        <v>2.2711</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4387</v>
+        <v>6.4579</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.6593</v>
+        <v>-4.1869</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5488</v>
+        <v>3.2741</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2207</v>
+        <v>2.319399999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6718000000000002</v>
+        <v>0.9544999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5751</v>
+        <v>-4.9879</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6554</v>
+        <v>-5.7205</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9196</v>
+        <v>0.7324999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3798</v>
+        <v>-0.9755</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9288</v>
+        <v>-2.5496</v>
       </c>
       <c r="L4" t="n">
-        <v>2.451</v>
+        <v>1.574</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1952000000000003</v>
+        <v>-4.0124</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2733</v>
+        <v>-3.1707</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4684999999999999</v>
+        <v>-0.8417</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8005</v>
+        <v>-0.7789000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4007</v>
+        <v>-10.5158</v>
       </c>
       <c r="R4" t="n">
-        <v>4.2012</v>
+        <v>9.736700000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8267</v>
+        <v>8.463000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3375</v>
+        <v>7.301399999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4892</v>
+        <v>1.1617</v>
       </c>
       <c r="V4" t="n">
-        <v>-2</v>
+        <v>0.5777999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5791</v>
+        <v>6.5095</v>
       </c>
       <c r="X4" t="n">
-        <v>-4.5789</v>
+        <v>-5.9316</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9885</v>
+        <v>2.8261</v>
       </c>
       <c r="E5" t="n">
-        <v>3.281</v>
+        <v>0.4942</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2925</v>
+        <v>2.332000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>4.300800000000001</v>
+        <v>8.437000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2201</v>
+        <v>1.0495</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0807</v>
+        <v>7.3877</v>
       </c>
       <c r="J5" t="n">
-        <v>7.5624</v>
+        <v>13.1281</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2794</v>
+        <v>4.0489</v>
       </c>
       <c r="L5" t="n">
-        <v>5.2831</v>
+        <v>9.0791</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.2617</v>
+        <v>-4.6909</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0592</v>
+        <v>-2.9995</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.2023</v>
+        <v>-1.6916</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6002</v>
+        <v>2.5315</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.601</v>
+        <v>-8.957800000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>4.2012</v>
+        <v>11.4894</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.273</v>
+        <v>-5.752</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.8802</v>
+        <v>-5.1766</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3926999999999999</v>
+        <v>-0.5754</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-2.3906</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1998</v>
+        <v>1.5006</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.8394</v>
+        <v>-3.8912</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>I. BOU MINARRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8731</v>
+        <v>0.3707</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003900000000000015</v>
+        <v>0.3321</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8692</v>
+        <v>0.0386</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3648</v>
+        <v>-0.1913</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1445</v>
+        <v>-0.0518</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2202</v>
+        <v>-0.1395</v>
       </c>
       <c r="J6" t="n">
-        <v>4.346399999999999</v>
+        <v>0.0205</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1028</v>
+        <v>0.0205</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2436</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01839999999999997</v>
+        <v>-0.2118</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9581999999999999</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9766</v>
+        <v>-0.1395</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.8011</v>
+        <v>0.1947</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.0018</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2006</v>
+        <v>0.1947</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6892</v>
+        <v>-0.1917</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3199</v>
+        <v>-0.2473</v>
       </c>
       <c r="U6" t="n">
-        <v>1.009</v>
+        <v>0.0557</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3798</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.9792</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. TORTAROLO</t>
+          <t>Q. GJENERALI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4427</v>
+        <v>-0.5123000000000004</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1641000000000004</v>
+        <v>-1.1192</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2786</v>
+        <v>0.607</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0188</v>
+        <v>2.2568</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1791999999999999</v>
+        <v>-0.9384</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1979</v>
+        <v>3.194999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8161</v>
+        <v>4.2654</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6869999999999999</v>
+        <v>2.4404</v>
       </c>
       <c r="L7" t="n">
-        <v>3.129</v>
+        <v>1.8249</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7974</v>
+        <v>-2.0088</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8662</v>
+        <v>-3.3788</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9311</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2000999999999999</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.401199999999999</v>
+        <v>-7.9842</v>
       </c>
       <c r="R7" t="n">
-        <v>4.6013</v>
+        <v>6.2316</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.1811</v>
+        <v>-2.8995</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1377</v>
+        <v>-1.9022</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.0434</v>
+        <v>-0.9973000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5196</v>
+        <v>1.8832</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5588</v>
+        <v>4.5016</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0392</v>
+        <v>-2.6186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0942</v>
+        <v>-2.803400000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4493</v>
+        <v>-3.7019</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6449</v>
+        <v>0.8984999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2237</v>
+        <v>-5.067299999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3829</v>
+        <v>-6.8134</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6067</v>
+        <v>1.7462</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5072000000000001</v>
+        <v>-1.7996</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4193</v>
+        <v>-3.2913</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9121</v>
+        <v>1.4919</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7309</v>
+        <v>-3.2677</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0364</v>
+        <v>-3.5221</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3054999999999999</v>
+        <v>0.2544000000000002</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8006</v>
+        <v>4.8685</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-3.3105</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8008</v>
+        <v>8.179</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0712</v>
+        <v>-2.2382</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0757</v>
+        <v>-0.3200999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004500000000000004</v>
+        <v>-1.918</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.5998</v>
+        <v>-0.3663</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1195</v>
+        <v>1.7285</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.7192</v>
+        <v>-2.0947</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1862</v>
+        <v>-2.8677</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5521</v>
+        <v>-2.595899999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3658000000000001</v>
+        <v>-0.2717999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7022</v>
+        <v>0.4497000000000002</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4895</v>
+        <v>0.4108999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7873000000000001</v>
+        <v>0.03870000000000029</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4998</v>
+        <v>2.5159</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8846</v>
+        <v>2.5789</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6152</v>
+        <v>-0.06309999999999993</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7975</v>
+        <v>-2.0663</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3951</v>
+        <v>-2.168</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4024</v>
+        <v>0.1017999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2003</v>
+        <v>-9.999999999971143e-05</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.4015</v>
+        <v>-9.542100000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>4.2012</v>
+        <v>9.542</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.0276</v>
+        <v>-1.9225</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.6293</v>
+        <v>-1.903</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3983</v>
+        <v>-0.01950000000000005</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3396</v>
+        <v>-1.3948</v>
       </c>
       <c r="W9" t="n">
-        <v>1.9792</v>
+        <v>6.3332</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-7.728</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9476</v>
+        <v>-2.9658</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7694</v>
+        <v>-4.988200000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1782</v>
+        <v>2.0224</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0822</v>
+        <v>3.7513</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.1282</v>
+        <v>-0.2198999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04610000000000003</v>
+        <v>3.9711</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5215</v>
+        <v>8.3003</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2413</v>
+        <v>3.2153</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7197</v>
+        <v>5.085</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5606</v>
+        <v>-4.5491</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.887</v>
+        <v>-3.4352</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6737</v>
+        <v>-1.114</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6004</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4007</v>
+        <v>-11.6842</v>
       </c>
       <c r="R10" t="n">
-        <v>4.0012</v>
+        <v>9.9315</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4456</v>
+        <v>-5.3658</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2864</v>
+        <v>-4.8333</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.159</v>
+        <v>-0.5327</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0203</v>
+        <v>0.4015</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4393</v>
+        <v>3.229</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4596</v>
+        <v>-2.8275</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,148 +1264,226 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4341</v>
+        <v>-8.1959</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.726</v>
+        <v>-11.2067</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2919</v>
+        <v>3.0107</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.9892</v>
+        <v>-5.9306</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5173000000000001</v>
+        <v>-4.7581</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.4718</v>
+        <v>-1.1724</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.888</v>
+        <v>-2.5775</v>
       </c>
       <c r="K11" t="n">
-        <v>0.14</v>
+        <v>-1.8416</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.028</v>
+        <v>-0.7359</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1011</v>
+        <v>-3.3531</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6573</v>
+        <v>-2.9168</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5562</v>
+        <v>-0.4363999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6002</v>
+        <v>-2.142</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2001</v>
+        <v>-11.2946</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8003</v>
+        <v>9.1526</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1547</v>
+        <v>3.1221</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6379</v>
+        <v>1.2682</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7926</v>
+        <v>1.854</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.1998</v>
+        <v>-3.2453</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.3974</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1998</v>
+        <v>-4.6426</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>J. GOMEZ CARBONELL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C.B. PUERTO SAGUNTO</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-15.7892</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-17.2158</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.4267</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-12.6172</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-5.3435</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-7.2738</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-13.2678</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-3.2686</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-9.9991</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.6503999999999999</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-2.0749</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.7252</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.5315</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-2.1421</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4.6736</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-1.7772</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1.8061</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.02879999999999999</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-3.9263</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-3.9263</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>C.B. PUERTO SAGUNTO</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-1.6355</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.757999999999999</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-4.393600000000001</v>
-      </c>
-      <c r="G12" t="n">
-        <v>8.814399999999999</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.068500000000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.745700000000001</v>
-      </c>
-      <c r="J12" t="n">
-        <v>22.4911</v>
-      </c>
-      <c r="K12" t="n">
-        <v>10.2604</v>
-      </c>
-      <c r="L12" t="n">
-        <v>12.2304</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-13.6765</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-8.191699999999999</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-5.4847</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.0005</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-32.0093</v>
-      </c>
-      <c r="R12" t="n">
-        <v>33.0094</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-9.0695</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-4.676299999999999</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-4.3931</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-2.380699999999999</v>
-      </c>
-      <c r="W12" t="n">
-        <v>16.953</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-19.3333</v>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-7.483400000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-19.69970000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12.2164</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-3.407399999999997</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-29.5858</v>
+      </c>
+      <c r="I13" t="n">
+        <v>26.1782</v>
+      </c>
+      <c r="J13" t="n">
+        <v>29.0646</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.6146999999999996</v>
+      </c>
+      <c r="L13" t="n">
+        <v>28.44970000000001</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-32.4724</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-30.2009</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-2.272200000000001</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10.7105</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-77.89450000000001</v>
+      </c>
+      <c r="R13" t="n">
+        <v>88.60480000000001</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-16.8154</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-11.7801</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-5.034999999999999</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.0294</v>
+      </c>
+      <c r="W13" t="n">
+        <v>40.9106</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-38.8812</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. PUERTO SAGUNTO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_C.B. PUERTO SAGUNTO.xlsx
@@ -565,13 +565,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>13.9368</v>
+        <v>14.7468</v>
       </c>
       <c r="E2" t="n">
-        <v>11.9897</v>
+        <v>11.8383</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9472</v>
+        <v>2.9086</v>
       </c>
       <c r="G2" t="n">
         <v>6.196899999999999</v>
@@ -610,13 +610,13 @@
         <v>11.6842</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.036</v>
+        <v>-2.2259</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9946999999999998</v>
+        <v>-1.1462</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.041</v>
+        <v>-1.0798</v>
       </c>
       <c r="V2" t="n">
         <v>7.6601</v>
@@ -643,13 +643,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2432</v>
+        <v>8.885300000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9926</v>
+        <v>8.3949</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7494000000000001</v>
+        <v>0.4903999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>4.2952</v>
@@ -688,13 +688,13 @@
         <v>7.7895</v>
       </c>
       <c r="S3" t="n">
-        <v>-5.2176</v>
+        <v>-1.5756</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.1664</v>
+        <v>-0.7641</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.0513</v>
+        <v>-0.8116</v>
       </c>
       <c r="V3" t="n">
         <v>2.2711</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2741</v>
+        <v>6.1356</v>
       </c>
       <c r="E4" t="n">
-        <v>2.319399999999999</v>
+        <v>3.3709</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9544999999999999</v>
+        <v>2.7646</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.9879</v>
+        <v>8.437000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.7205</v>
+        <v>1.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7324999999999999</v>
+        <v>7.3877</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9755</v>
+        <v>13.1281</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.5496</v>
+        <v>4.0489</v>
       </c>
       <c r="L4" t="n">
-        <v>1.574</v>
+        <v>9.0791</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.0124</v>
+        <v>-4.6909</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.1707</v>
+        <v>-2.9995</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8417</v>
+        <v>-1.6916</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7789000000000001</v>
+        <v>2.5315</v>
       </c>
       <c r="Q4" t="n">
-        <v>-10.5158</v>
+        <v>-8.957800000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>9.736700000000001</v>
+        <v>11.4894</v>
       </c>
       <c r="S4" t="n">
-        <v>8.463000000000001</v>
+        <v>-2.4425</v>
       </c>
       <c r="T4" t="n">
-        <v>7.301399999999999</v>
+        <v>-2.2998</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1617</v>
+        <v>-0.1427</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5777999999999999</v>
+        <v>-2.3906</v>
       </c>
       <c r="W4" t="n">
-        <v>6.5095</v>
+        <v>1.5006</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.9316</v>
+        <v>-3.8912</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>Q. GJENERALI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8261</v>
+        <v>0.6153000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4942</v>
+        <v>-0.2359999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>2.332000000000001</v>
+        <v>0.8513000000000002</v>
       </c>
       <c r="G5" t="n">
-        <v>8.437000000000001</v>
+        <v>2.2568</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0495</v>
+        <v>-0.9384</v>
       </c>
       <c r="I5" t="n">
-        <v>7.3877</v>
+        <v>3.194999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>13.1281</v>
+        <v>4.2654</v>
       </c>
       <c r="K5" t="n">
-        <v>4.0489</v>
+        <v>2.4404</v>
       </c>
       <c r="L5" t="n">
-        <v>9.0791</v>
+        <v>1.8249</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.6909</v>
+        <v>-2.0088</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.9995</v>
+        <v>-3.3788</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6916</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5315</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q5" t="n">
-        <v>-8.957800000000001</v>
+        <v>-7.9842</v>
       </c>
       <c r="R5" t="n">
-        <v>11.4894</v>
+        <v>6.2316</v>
       </c>
       <c r="S5" t="n">
-        <v>-5.752</v>
+        <v>-1.772</v>
       </c>
       <c r="T5" t="n">
-        <v>-5.1766</v>
+        <v>-1.0188</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5754</v>
+        <v>-0.7530999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.3906</v>
+        <v>1.8832</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5006</v>
+        <v>4.5016</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.8912</v>
+        <v>-2.6186</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3707</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3321</v>
+        <v>0.4318</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0386</v>
+        <v>0.122</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1913</v>
@@ -922,13 +922,13 @@
         <v>0.1947</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1917</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2473</v>
+        <v>-0.1477</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0557</v>
+        <v>0.1391</v>
       </c>
       <c r="V6" t="n">
         <v>0.5590000000000001</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q. GJENERALI</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5123000000000004</v>
+        <v>0.06109999999999971</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1192</v>
+        <v>-2.3726</v>
       </c>
       <c r="F7" t="n">
-        <v>0.607</v>
+        <v>2.4336</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2568</v>
+        <v>3.7513</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9384</v>
+        <v>-0.2198999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>3.194999999999999</v>
+        <v>3.9711</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2654</v>
+        <v>8.3003</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4404</v>
+        <v>3.2153</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8249</v>
+        <v>5.085</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0088</v>
+        <v>-4.5491</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.3788</v>
+        <v>-3.4352</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>-1.114</v>
       </c>
       <c r="P7" t="n">
         <v>-1.7526</v>
       </c>
       <c r="Q7" t="n">
-        <v>-7.9842</v>
+        <v>-11.6842</v>
       </c>
       <c r="R7" t="n">
-        <v>6.2316</v>
+        <v>9.9315</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.8995</v>
+        <v>-2.3391</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.9022</v>
+        <v>-2.2176</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9973000000000001</v>
+        <v>-0.1215</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8832</v>
+        <v>0.4015</v>
       </c>
       <c r="W7" t="n">
-        <v>4.5016</v>
+        <v>3.229</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.6186</v>
+        <v>-2.8275</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.803400000000001</v>
+        <v>-2.936900000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.7019</v>
+        <v>-4.351599999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8984999999999999</v>
+        <v>1.4146</v>
       </c>
       <c r="G8" t="n">
         <v>-5.067299999999999</v>
@@ -1078,13 +1078,13 @@
         <v>8.179</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.2382</v>
+        <v>-2.3717</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3200999999999999</v>
+        <v>-0.9699</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.918</v>
+        <v>-1.4019</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3663</v>
@@ -1111,13 +1111,13 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8677</v>
+        <v>-3.0306</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.595899999999999</v>
+        <v>-2.585900000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2717999999999999</v>
+        <v>-0.4448000000000005</v>
       </c>
       <c r="G9" t="n">
         <v>0.4497000000000002</v>
@@ -1156,13 +1156,13 @@
         <v>9.542</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9225</v>
+        <v>-2.0855</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.903</v>
+        <v>-1.8929</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.01950000000000005</v>
+        <v>-0.1928</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3948</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9658</v>
+        <v>-3.6263</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.988200000000001</v>
+        <v>-3.3998</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0224</v>
+        <v>-0.2266</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7513</v>
+        <v>-4.9879</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2198999999999999</v>
+        <v>-5.7205</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9711</v>
+        <v>0.7324999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>8.3003</v>
+        <v>-0.9755</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2153</v>
+        <v>-2.5496</v>
       </c>
       <c r="L10" t="n">
-        <v>5.085</v>
+        <v>1.574</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.5491</v>
+        <v>-4.0124</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.4352</v>
+        <v>-3.1707</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.114</v>
+        <v>-0.8417</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7526</v>
+        <v>-0.7789000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-11.6842</v>
+        <v>-10.5158</v>
       </c>
       <c r="R10" t="n">
-        <v>9.9315</v>
+        <v>9.736700000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.3658</v>
+        <v>1.5625</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.8333</v>
+        <v>1.582</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5327</v>
+        <v>-0.01940000000000006</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4015</v>
+        <v>0.5777999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>3.229</v>
+        <v>6.5095</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.8275</v>
+        <v>-5.9316</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.1959</v>
+        <v>-10.325</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.2067</v>
+        <v>-12.5782</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0107</v>
+        <v>2.2532</v>
       </c>
       <c r="G11" t="n">
         <v>-5.9306</v>
@@ -1312,13 +1312,13 @@
         <v>9.1526</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1221</v>
+        <v>0.9931999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2682</v>
+        <v>-0.1032</v>
       </c>
       <c r="U11" t="n">
-        <v>1.854</v>
+        <v>1.0963</v>
       </c>
       <c r="V11" t="n">
         <v>-3.2453</v>
@@ -1345,13 +1345,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.7892</v>
+        <v>-14.7137</v>
       </c>
       <c r="E12" t="n">
-        <v>-17.2158</v>
+        <v>-16.3568</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4267</v>
+        <v>1.643</v>
       </c>
       <c r="G12" t="n">
         <v>-12.6172</v>
@@ -1390,13 +1390,13 @@
         <v>4.6736</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7772</v>
+        <v>-0.7015</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.8061</v>
+        <v>-0.9469</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02879999999999999</v>
+        <v>0.2452</v>
       </c>
       <c r="V12" t="n">
         <v>-3.9263</v>
@@ -1423,13 +1423,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.483400000000001</v>
+        <v>-3.634499999999996</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.69970000000001</v>
+        <v>-17.845</v>
       </c>
       <c r="F13" t="n">
-        <v>12.2164</v>
+        <v>14.2099</v>
       </c>
       <c r="G13" t="n">
         <v>-3.407399999999997</v>
@@ -1447,7 +1447,7 @@
         <v>0.6146999999999996</v>
       </c>
       <c r="L13" t="n">
-        <v>28.44970000000001</v>
+        <v>28.4497</v>
       </c>
       <c r="M13" t="n">
         <v>-32.4724</v>
@@ -1456,7 +1456,7 @@
         <v>-30.2009</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.272200000000001</v>
+        <v>-2.272200000000002</v>
       </c>
       <c r="P13" t="n">
         <v>10.7105</v>
@@ -1465,16 +1465,16 @@
         <v>-77.89450000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>88.60480000000001</v>
+        <v>88.60479999999998</v>
       </c>
       <c r="S13" t="n">
-        <v>-16.8154</v>
+        <v>-12.9666</v>
       </c>
       <c r="T13" t="n">
-        <v>-11.7801</v>
+        <v>-9.925099999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.034999999999999</v>
+        <v>-3.0422</v>
       </c>
       <c r="V13" t="n">
         <v>2.0294</v>
@@ -1483,7 +1483,7 @@
         <v>40.9106</v>
       </c>
       <c r="X13" t="n">
-        <v>-38.8812</v>
+        <v>-38.88119999999999</v>
       </c>
     </row>
   </sheetData>
